--- a/forms/trg/Formulir_TRG_constitution.xlsx
+++ b/forms/trg/Formulir_TRG_constitution.xlsx
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="B26" s="7">
-        <f>COUNTA(Anggota!B5:B22)</f>
+        <f>COUNTA(Anggota!B5:B23)</f>
         <v/>
       </c>
     </row>
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="B27" s="7">
-        <f>COUNTA(Anggota!F5:F22)</f>
+        <f>COUNTA(Anggota!F5:F23)</f>
         <v/>
       </c>
     </row>
@@ -832,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -937,12 +937,12 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Ahsan Yunus, S.H., M.H.</t>
+          <t>Dr. Naswar, S.H., M.H.</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="12" t="n"/>
@@ -966,12 +966,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Arini Nur Annisa, S.H., M.H.</t>
+          <t>Ahsan Yunus, S.H., M.H.</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="12" t="n"/>
@@ -995,12 +995,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Ariani Arifin, S.H., M.H</t>
+          <t>Arini Nur Annisa, S.H., M.H.</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="12" t="n"/>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Assoc. Prof. Vilard Bytyqi, Ph.D</t>
+          <t>Ariani Arifin, S.H., M.H</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="12" t="n"/>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Fakhril Riadi, S.H., M.H.</t>
+          <t>Assoc. Prof. Vilard Bytyqi, Ph.D</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D9" s="12" t="n"/>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Muh. Dirga Ravli, S.H.</t>
+          <t>Fakhril Riadi, S.H., M.H.</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D10" s="12" t="n"/>
@@ -1109,10 +1109,22 @@
       <c r="A11" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="12" t="n"/>
-      <c r="C11" s="12" t="n"/>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Muh. Dirga Ravli, S.H.</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
       <c r="D11" s="12" t="n"/>
-      <c r="E11" s="11" t="n"/>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>The Constitutional Convention and Democracy Research Group examines the evolving relationship between constitutional frameworks and democratic governance.</t>
+        </is>
+      </c>
       <c r="F11" s="12" t="n"/>
       <c r="G11" s="12" t="n"/>
       <c r="H11" s="12" t="n"/>
@@ -1120,7 +1132,11 @@
       <c r="J11" s="12" t="n"/>
       <c r="K11" s="12" t="n"/>
       <c r="L11" s="12" t="n"/>
-      <c r="M11" s="12" t="n"/>
+      <c r="M11" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -1309,15 +1325,32 @@
       <c r="L22" s="12" t="n"/>
       <c r="M22" s="12" t="n"/>
     </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="12" t="n"/>
+      <c r="C23" s="12" t="n"/>
+      <c r="D23" s="12" t="n"/>
+      <c r="E23" s="11" t="n"/>
+      <c r="F23" s="12" t="n"/>
+      <c r="G23" s="12" t="n"/>
+      <c r="H23" s="12" t="n"/>
+      <c r="I23" s="12" t="n"/>
+      <c r="J23" s="12" t="n"/>
+      <c r="K23" s="12" t="n"/>
+      <c r="L23" s="12" t="n"/>
+      <c r="M23" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
